--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -413,38 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -456,26 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.50388</v>
+        <v>125.92234</v>
       </c>
       <c r="D2" t="n">
-        <v>17.38113</v>
+        <v>90.88558</v>
       </c>
       <c r="E2" t="n">
-        <v>17.53062</v>
+        <v>97.20971</v>
       </c>
       <c r="F2" t="n">
-        <v>45.06457</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.89093</v>
+        <v>550.5542799999999</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.87614</v>
+        <v>127.56862</v>
       </c>
       <c r="D3" t="n">
-        <v>17.43896</v>
+        <v>89.01078</v>
       </c>
       <c r="E3" t="n">
-        <v>17.77036</v>
+        <v>95.0112</v>
       </c>
       <c r="F3" t="n">
-        <v>45.32798</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05259</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.90486</v>
+        <v>541.0049299999999</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.80934</v>
+        <v>126.00457</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33669</v>
+        <v>90.59596000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>17.98502</v>
+        <v>96.15051</v>
       </c>
       <c r="F4" t="n">
-        <v>43.67183</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05397</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.90518</v>
+        <v>538.42141</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +507,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.76171</v>
+        <v>128.90893</v>
       </c>
       <c r="D5" t="n">
-        <v>17.32965</v>
+        <v>90.43214</v>
       </c>
       <c r="E5" t="n">
-        <v>17.30361</v>
+        <v>94.33275</v>
       </c>
       <c r="F5" t="n">
-        <v>44.15515</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.89574</v>
+        <v>549.35653</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +526,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.54866</v>
+        <v>125.30488</v>
       </c>
       <c r="D6" t="n">
-        <v>17.19313</v>
+        <v>88.46581</v>
       </c>
       <c r="E6" t="n">
-        <v>17.76905</v>
+        <v>96.81948</v>
       </c>
       <c r="F6" t="n">
-        <v>44.04888</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05325</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.91205</v>
+        <v>540.40054</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.48734</v>
+        <v>123.71105</v>
       </c>
       <c r="D7" t="n">
-        <v>17.16069</v>
+        <v>91.69002999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>17.53836</v>
+        <v>96.23446</v>
       </c>
       <c r="F7" t="n">
-        <v>44.24787</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.05379</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.91399</v>
+        <v>534.38377</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.48958</v>
+        <v>127.2143</v>
       </c>
       <c r="D8" t="n">
-        <v>17.01748</v>
+        <v>89.58257999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>17.04642</v>
+        <v>95.91557</v>
       </c>
       <c r="F8" t="n">
-        <v>44.41975</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05304</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.91908</v>
+        <v>538.32044</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.08004</v>
+        <v>126.92372</v>
       </c>
       <c r="D9" t="n">
-        <v>17.09961</v>
+        <v>90.59408000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>17.54261</v>
+        <v>96.75064999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>44.54134</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05214</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.89328</v>
+        <v>526.73128</v>
       </c>
     </row>
     <row r="10">
@@ -660,48 +602,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.71599</v>
+        <v>123.90383</v>
       </c>
       <c r="D10" t="n">
-        <v>17.16968</v>
+        <v>90.96216</v>
       </c>
       <c r="E10" t="n">
-        <v>17.31169</v>
+        <v>94.19513000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>45.03314</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05427</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.87669</v>
+        <v>533.79338</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Diameter</t>
         </is>
       </c>
     </row>
@@ -713,8 +634,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Micro Bump 3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8.92431</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25.52387</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +650,12 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>9.14099</v>
+      </c>
+      <c r="D13" t="n">
+        <v>25.19035</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +663,12 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>8.962260000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25.23878</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +676,12 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>9.057550000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.50673</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +689,12 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>9.05538</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.65482</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +702,12 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>8.988569999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25.65443</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +715,12 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>8.85876</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25.61374</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,6 +728,12 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>9.06959</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25.24548</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -772,46 +741,42 @@
           <t>Unit 3</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>8.9756</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.72395</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -823,32 +788,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.78293</v>
+        <v>17.76186</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08488999999999999</v>
+        <v>17.39154</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6291600000000001</v>
+        <v>17.59195</v>
       </c>
       <c r="F22" t="n">
-        <v>1.01041</v>
+        <v>43.82567</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11535</v>
+        <v>0.05337</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09753000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13369</v>
+        <v>1.89604</v>
       </c>
     </row>
     <row r="23">
@@ -858,28 +817,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.79325</v>
+        <v>18.02593</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08558</v>
+        <v>17.32297</v>
       </c>
       <c r="E23" t="n">
-        <v>0.64151</v>
+        <v>17.60655</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0154</v>
+        <v>44.48381</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11507</v>
+        <v>0.05327</v>
       </c>
       <c r="H23" t="n">
-        <v>0.008030000000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09906</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13423</v>
+        <v>1.92296</v>
       </c>
     </row>
     <row r="24">
@@ -889,28 +842,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.77542</v>
+        <v>17.60241</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08470999999999999</v>
+        <v>17.25096</v>
       </c>
       <c r="E24" t="n">
-        <v>0.65429</v>
+        <v>17.4922</v>
       </c>
       <c r="F24" t="n">
-        <v>1.00265</v>
+        <v>43.86178</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11581</v>
+        <v>0.05349</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00812</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09666</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13142</v>
+        <v>1.93466</v>
       </c>
     </row>
     <row r="25">
@@ -920,28 +867,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7880200000000001</v>
+        <v>17.53352</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08548</v>
+        <v>16.91659</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6332100000000001</v>
+        <v>17.3508</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99782</v>
+        <v>44.79254</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11189</v>
+        <v>0.05339</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00804</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09702</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.13227</v>
+        <v>1.88392</v>
       </c>
     </row>
     <row r="26">
@@ -951,28 +892,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.77227</v>
+        <v>17.65621</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08498</v>
+        <v>17.17741</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6151799999999999</v>
+        <v>17.40189</v>
       </c>
       <c r="F26" t="n">
-        <v>1.00322</v>
+        <v>44.36508</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11666</v>
+        <v>0.05446</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00814</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09676999999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13473</v>
+        <v>1.89947</v>
       </c>
     </row>
     <row r="27">
@@ -982,28 +917,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.76051</v>
+        <v>17.7536</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08248</v>
+        <v>17.3019</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6463100000000001</v>
+        <v>17.60501</v>
       </c>
       <c r="F27" t="n">
-        <v>1.01297</v>
+        <v>43.96583</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11428</v>
+        <v>0.05301</v>
       </c>
       <c r="H27" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09737</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13275</v>
+        <v>1.91464</v>
       </c>
     </row>
     <row r="28">
@@ -1013,28 +942,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7904099999999999</v>
+        <v>17.53223</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08434</v>
+        <v>17.36545</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6308</v>
+        <v>17.44799</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0339</v>
+        <v>44.62439</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11539</v>
+        <v>0.05444</v>
       </c>
       <c r="H28" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09837</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13319</v>
+        <v>1.89783</v>
       </c>
     </row>
     <row r="29">
@@ -1044,28 +967,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7710399999999999</v>
+        <v>17.77844</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08581</v>
+        <v>17.46429</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6375999999999999</v>
+        <v>17.72801</v>
       </c>
       <c r="F29" t="n">
-        <v>1.01145</v>
+        <v>44.20757</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11324</v>
+        <v>0.05176</v>
       </c>
       <c r="H29" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09801</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13318</v>
+        <v>1.87479</v>
       </c>
     </row>
     <row r="30">
@@ -1075,28 +992,348 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76685</v>
+        <v>17.91707</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08448</v>
+        <v>17.47299</v>
       </c>
       <c r="E30" t="n">
-        <v>0.63544</v>
+        <v>17.48557</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9896</v>
+        <v>44.83778</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11183</v>
+        <v>0.05335</v>
       </c>
       <c r="H30" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09970999999999999</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13096</v>
+        <v>1.86967</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.80421</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08297</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6438</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.01791</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11405</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09778000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.77458</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08543000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.64936</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.00231</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09644999999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.13412</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.78147</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08452999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.64012</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.01171</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11432</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09718</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1336</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7791400000000001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.64102</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.0177</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11742</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09866</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.13305</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.77829</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08486</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.64307</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11502</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09778000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.13562</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.78366</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.62329</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.01023</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11555</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00797</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09725</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.13228</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.78067</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08427</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.65032</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.01223</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11441</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00797</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.13098</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6375999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.00921</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11393</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09805</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13221</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.78574</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.62749</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.98584</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11366</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09728000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.13302</v>
       </c>
     </row>
   </sheetData>
